--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486467_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486467_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.185</v>
+        <v>2.501</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7452</v>
+        <v>2.9688</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5602</v>
+        <v>-0.4678</v>
       </c>
       <c r="G2" t="n">
         <v>0.9661999999999999</v>
@@ -610,13 +610,13 @@
         <v>0.435</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1064</v>
+        <v>-0.7904</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6165</v>
+        <v>-0.3929</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4899</v>
+        <v>-0.3975</v>
       </c>
       <c r="V2" t="n">
         <v>1.8902</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1906</v>
+        <v>1.4488</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4577</v>
+        <v>4.346</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.2671</v>
+        <v>-2.8972</v>
       </c>
       <c r="G3" t="n">
         <v>3.3521</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7434</v>
+        <v>-1.4853</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4194</v>
+        <v>-0.5311</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.324</v>
+        <v>-0.9542</v>
       </c>
       <c r="V3" t="n">
         <v>0.452</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.083</v>
+        <v>1.1529</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6205</v>
+        <v>-1.1949</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5375</v>
+        <v>2.3478</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2317</v>
+        <v>1.6069</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3496</v>
+        <v>0.8212</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8821</v>
+        <v>0.7857</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2948</v>
+        <v>0.4731</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2039</v>
+        <v>0.2436</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0909</v>
+        <v>0.2295</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0631</v>
+        <v>1.1338</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1457</v>
+        <v>0.5776</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2088</v>
+        <v>0.5562</v>
       </c>
       <c r="P4" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09420000000000001</v>
+        <v>-0.4539</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3257</v>
+        <v>-0.5804</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2315</v>
+        <v>0.1265</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.678</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9833</v>
+        <v>0.3122</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6419</v>
+        <v>0.7264</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6252</v>
+        <v>-0.4143</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6069</v>
+        <v>1.2317</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8212</v>
+        <v>0.3496</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7857</v>
+        <v>0.8821</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4731</v>
+        <v>1.2948</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2436</v>
+        <v>0.2039</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2295</v>
+        <v>1.0909</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1338</v>
+        <v>-0.0631</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5776</v>
+        <v>0.1457</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5562</v>
+        <v>-0.2088</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6236</v>
+        <v>-0.6766</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0274</v>
+        <v>-0.5684</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4039</v>
+        <v>-0.1082</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.678</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.678</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7437</v>
+        <v>-0.867</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2055</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5382</v>
+        <v>-0.6615</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5004</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2432</v>
+        <v>-0.3665</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2055</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0377</v>
+        <v>-0.161</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9646</v>
+        <v>-1.8837</v>
       </c>
       <c r="E7" t="n">
-        <v>1.702</v>
+        <v>1.8137</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.6666</v>
+        <v>-3.6974</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7227</v>
@@ -1000,13 +1000,13 @@
         <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4986</v>
+        <v>-1.4177</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.822</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6767</v>
+        <v>-0.7075</v>
       </c>
       <c r="V7" t="n">
         <v>0.8218</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4911</v>
+        <v>-2.9149</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1023</v>
+        <v>-3.8788</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6111</v>
+        <v>0.9639</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3071</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0482</v>
+        <v>-0.472</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8904</v>
+        <v>-0.6669</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.195</v>
       </c>
       <c r="V9" t="n">
         <v>1.3867</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9551</v>
+        <v>-3.0726</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3631</v>
+        <v>-0.8287</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.592</v>
+        <v>-2.2439</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2134</v>
+        <v>-2.5158</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.0564</v>
+        <v>-0.0152</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.157</v>
+        <v>-2.5005</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3901</v>
+        <v>-0.616</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.889</v>
+        <v>0.9307</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4989</v>
+        <v>-1.5467</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8233</v>
+        <v>-1.8998</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1674</v>
+        <v>-0.9459</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6558</v>
+        <v>-0.9539</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0413</v>
+        <v>-0.4491</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9421</v>
+        <v>-0.2127</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09909999999999999</v>
+        <v>-0.2364</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7395</v>
+        <v>-0.7602</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5204</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6236</v>
+        <v>-3.3079</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1639</v>
+        <v>-0.7146</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4597</v>
+        <v>-2.5933</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5158</v>
+        <v>1.6678</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0152</v>
+        <v>-0.0335</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5005</v>
+        <v>1.7013</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.616</v>
+        <v>3.6259</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9307</v>
+        <v>0.3348</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5467</v>
+        <v>3.2911</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8998</v>
+        <v>-1.9581</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9459</v>
+        <v>-0.3683</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9539</v>
+        <v>-1.5898</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6525</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0002</v>
+        <v>-1.5577</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.548</v>
+        <v>-1.0779</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4522</v>
+        <v>-0.4798</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7602</v>
+        <v>-1.243</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7602</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6856</v>
+        <v>-3.8915</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9381</v>
+        <v>-2.1454</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7474</v>
+        <v>-1.7461</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6678</v>
+        <v>-3.2134</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0335</v>
+        <v>-3.0564</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7013</v>
+        <v>-0.157</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6259</v>
+        <v>-2.3901</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3348</v>
+        <v>-2.889</v>
       </c>
       <c r="L12" t="n">
-        <v>3.2911</v>
+        <v>0.4989</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9581</v>
+        <v>-0.8233</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3683</v>
+        <v>-0.1674</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5898</v>
+        <v>-0.6558</v>
       </c>
       <c r="P12" t="n">
+        <v>-1.5225</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-2.1751</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9353</v>
+        <v>0.1048</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3014</v>
+        <v>0.1598</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6339</v>
+        <v>-0.055</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.243</v>
+        <v>0.7395</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.243</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5863</v>
+        <v>-4.0854</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0307</v>
+        <v>-2.8072</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5556</v>
+        <v>-1.2782</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4935</v>
@@ -1468,13 +1468,13 @@
         <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4626</v>
+        <v>-0.9617</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.5299</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7091</v>
+        <v>-0.4317</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1952</v>
@@ -1504,16 +1504,16 @@
         <v>-16.7339</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.9595</v>
+        <v>-2.9596</v>
       </c>
       <c r="F14" t="n">
         <v>-13.7744</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.1719</v>
+        <v>-5.171899999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2428000000000002</v>
+        <v>0.2428</v>
       </c>
       <c r="I14" t="n">
         <v>-5.4146</v>
@@ -1522,10 +1522,10 @@
         <v>6.567299999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3438</v>
+        <v>2.343800000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>4.2236</v>
+        <v>4.223600000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-11.7393</v>
@@ -1537,7 +1537,7 @@
         <v>-9.638300000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.3501</v>
+        <v>-4.350099999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.9629</v>
@@ -1546,22 +1546,22 @@
         <v>7.612499999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.6256</v>
+        <v>-9.625700000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.8643</v>
+        <v>-5.864100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.7614</v>
+        <v>-3.761400000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>2.413799999999999</v>
+        <v>2.4138</v>
       </c>
       <c r="W14" t="n">
         <v>8.3003</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.886500000000001</v>
+        <v>-5.8865</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.6226</v>
+        <v>9.6244</v>
       </c>
       <c r="E15" t="n">
-        <v>8.8203</v>
+        <v>9.2674</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1978</v>
+        <v>0.357</v>
       </c>
       <c r="G15" t="n">
         <v>9.8902</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2225</v>
+        <v>0.7793</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1454</v>
+        <v>0.3016</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0772</v>
+        <v>0.4777</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0444</v>
+        <v>4.7959</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5471</v>
+        <v>4.3294</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4972</v>
+        <v>0.4664</v>
       </c>
       <c r="G16" t="n">
         <v>2.5114</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2501</v>
+        <v>0.5014</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8099</v>
+        <v>-0.0276</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5599</v>
+        <v>0.529</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1745</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6331</v>
+        <v>3.8951</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9681</v>
+        <v>1.6742</v>
       </c>
       <c r="F17" t="n">
-        <v>0.665</v>
+        <v>2.2209</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1325</v>
+        <v>0.6569</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0519</v>
+        <v>-0.0579</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0806</v>
+        <v>0.7148</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3907</v>
+        <v>0.967</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4102</v>
+        <v>0.2769</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8009</v>
+        <v>0.6901</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2583</v>
+        <v>-0.3101</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4621</v>
+        <v>-0.3348</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7204</v>
+        <v>0.0247</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4354</v>
+        <v>1.5204</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8172</v>
+        <v>0.5119</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6182</v>
+        <v>1.0085</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3698</v>
+        <v>0.1952</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7602</v>
+        <v>0.1952</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.2669</v>
+        <v>2.978</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8919</v>
+        <v>2.7446</v>
       </c>
       <c r="F18" t="n">
-        <v>2.375</v>
+        <v>0.2334</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6569</v>
+        <v>1.1325</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0579</v>
+        <v>0.0519</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7148</v>
+        <v>1.0806</v>
       </c>
       <c r="J18" t="n">
-        <v>0.967</v>
+        <v>1.3907</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2769</v>
+        <v>-0.4102</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6901</v>
+        <v>1.8009</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3101</v>
+        <v>-0.2583</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3348</v>
+        <v>0.4621</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0247</v>
+        <v>-0.7204</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8923</v>
+        <v>1.7803</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2704</v>
+        <v>0.5936</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1626</v>
+        <v>1.1867</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4269</v>
+        <v>1.4789</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5736</v>
+        <v>0.9031</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8532</v>
+        <v>0.5758</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3545</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7161</v>
+        <v>0.7682</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8292</v>
+        <v>0.1586</v>
       </c>
       <c r="U19" t="n">
-        <v>0.887</v>
+        <v>0.6096</v>
       </c>
       <c r="V19" t="n">
         <v>0.1952</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2041</v>
+        <v>1.1602</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6042</v>
+        <v>0.3363</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>0.824</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9187</v>
+        <v>-1.6936</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4198</v>
+        <v>-1.2744</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4989</v>
+        <v>-0.4191</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2444</v>
+        <v>-0.7228</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.5504</v>
+        <v>-0.3436</v>
       </c>
       <c r="L20" t="n">
-        <v>0.306</v>
+        <v>-0.3793</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6742</v>
+        <v>-0.9707</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1306</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.0399</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>5.3626</v>
+        <v>-0.0162</v>
       </c>
       <c r="T20" t="n">
-        <v>4.3934</v>
+        <v>-0.0709</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9692</v>
+        <v>0.0547</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3698</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3698</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1256</v>
+        <v>1.1371</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0167</v>
+        <v>0.9049</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1089</v>
+        <v>0.2322</v>
       </c>
       <c r="G21" t="n">
         <v>1.0193</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3237</v>
+        <v>0.3353</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3461</v>
+        <v>0.2343</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0224</v>
+        <v>0.1009</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4633</v>
+        <v>0.34</v>
       </c>
       <c r="E22" t="n">
         <v>0.584</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1207</v>
+        <v>-0.244</v>
       </c>
       <c r="G22" t="n">
         <v>0.5505</v>
@@ -2170,13 +2170,13 @@
         <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2603</v>
+        <v>0.137</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2603</v>
+        <v>0.137</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5649999999999999</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>O. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3048</v>
+        <v>0.2719</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3343</v>
+        <v>0.0365</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6391</v>
+        <v>0.2354</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6936</v>
+        <v>0.003</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2744</v>
+        <v>-0.146</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4191</v>
+        <v>0.149</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7228</v>
+        <v>0.0365</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3436</v>
+        <v>0.0365</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3793</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9707</v>
+        <v>-0.0335</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.1825</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0399</v>
+        <v>0.149</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8717</v>
+        <v>0.0514</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1303</v>
+        <v>0.0514</v>
       </c>
       <c r="V23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>O. GOMEZ FERNANDEZ</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2411</v>
+        <v>-0.6322</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0365</v>
+        <v>-2.078</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2046</v>
+        <v>1.4458</v>
       </c>
       <c r="G24" t="n">
-        <v>0.003</v>
+        <v>-1.9187</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.146</v>
+        <v>-1.4198</v>
       </c>
       <c r="I24" t="n">
-        <v>0.149</v>
+        <v>-0.4989</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0365</v>
+        <v>-1.2444</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0365</v>
+        <v>-1.5504</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.306</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0335</v>
+        <v>-0.6742</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1825</v>
+        <v>0.1306</v>
       </c>
       <c r="O24" t="n">
-        <v>0.149</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0205</v>
+        <v>2.5263</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.7112</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0205</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3657</v>
+        <v>-3.622</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4706</v>
+        <v>-1.9118</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8951</v>
+        <v>-1.7102</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0356</v>
@@ -2404,13 +2404,13 @@
         <v>1.305</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1473</v>
+        <v>0.8911</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0649</v>
+        <v>0.4939</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2122</v>
+        <v>0.3972</v>
       </c>
       <c r="V25" t="n">
         <v>-1.695</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.233</v>
+        <v>-4.6935</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.4631</v>
+        <v>-3.0161</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7699</v>
+        <v>-1.6774</v>
       </c>
       <c r="G26" t="n">
         <v>-3.5896</v>
@@ -2482,13 +2482,13 @@
         <v>0.435</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1883</v>
+        <v>0.3512</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5924</v>
+        <v>-0.1454</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4041</v>
+        <v>0.4966</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8902</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>16.7341</v>
+        <v>16.7338</v>
       </c>
       <c r="E27" t="n">
-        <v>13.7744</v>
+        <v>13.7745</v>
       </c>
       <c r="F27" t="n">
-        <v>2.959499999999999</v>
+        <v>2.959299999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>5.1718</v>
+        <v>5.171800000000002</v>
       </c>
       <c r="H27" t="n">
         <v>-0.2426999999999997</v>
@@ -2536,7 +2536,7 @@
         <v>11.7392</v>
       </c>
       <c r="K27" t="n">
-        <v>2.101000000000001</v>
+        <v>2.101</v>
       </c>
       <c r="L27" t="n">
         <v>9.638299999999999</v>
@@ -2548,10 +2548,10 @@
         <v>-2.3437</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.223599999999999</v>
+        <v>-4.2236</v>
       </c>
       <c r="P27" t="n">
-        <v>4.350099999999999</v>
+        <v>4.3501</v>
       </c>
       <c r="Q27" t="n">
         <v>-7.6127</v>
@@ -2560,19 +2560,19 @@
         <v>11.9627</v>
       </c>
       <c r="S27" t="n">
-        <v>9.625599999999999</v>
+        <v>9.6257</v>
       </c>
       <c r="T27" t="n">
-        <v>3.7615</v>
+        <v>3.7612</v>
       </c>
       <c r="U27" t="n">
-        <v>5.8641</v>
+        <v>5.864299999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-2.4139</v>
       </c>
       <c r="W27" t="n">
-        <v>5.886399999999999</v>
+        <v>5.8864</v>
       </c>
       <c r="X27" t="n">
         <v>-8.3004</v>
